--- a/12610693.xlsx
+++ b/12610693.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -260,10 +260,25 @@
     <t>felt high energy</t>
   </si>
   <si>
-    <t>tired</t>
+    <t>feeling good</t>
   </si>
   <si>
-    <t>feeling good</t>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">felt fresh after morning walk </t>
+  </si>
+  <si>
+    <t xml:space="preserve">not felling much </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rest day </t>
+  </si>
+  <si>
+    <t>overwhelmed by today class schedule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enery remains low at the begining of week </t>
   </si>
 </sst>
 </file>
@@ -1334,21 +1349,21 @@
         <v>90</v>
       </c>
       <c r="F12" s="14">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G12" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H12" s="14">
         <v>30</v>
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>1090</v>
+        <v>790</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>350</v>
+        <v>650</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>64</v>
@@ -1380,21 +1395,21 @@
         <v>120</v>
       </c>
       <c r="F13" s="14">
+        <v>300</v>
+      </c>
+      <c r="G13" s="14">
         <v>6</v>
-      </c>
-      <c r="G13" s="14">
-        <v>300</v>
       </c>
       <c r="H13" s="14">
         <v>90</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>771</v>
+        <v>1065</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>669</v>
+        <v>375</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>64</v>
@@ -1426,21 +1441,21 @@
         <v>90</v>
       </c>
       <c r="F14" s="14">
+        <v>400</v>
+      </c>
+      <c r="G14" s="14">
         <v>8</v>
-      </c>
-      <c r="G14" s="14">
-        <v>400</v>
       </c>
       <c r="H14" s="14">
         <v>60</v>
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>758</v>
+        <v>1150</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>682</v>
+        <v>290</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>68</v>
@@ -1472,21 +1487,21 @@
         <v>120</v>
       </c>
       <c r="F15" s="14">
-        <v>8</v>
+        <v>250</v>
       </c>
       <c r="G15" s="14">
-        <v>400</v>
+        <v>5</v>
       </c>
       <c r="H15" s="14">
         <v>30</v>
       </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>668</v>
+        <v>910</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>772</v>
+        <v>530</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>55</v>
@@ -1518,21 +1533,21 @@
         <v>120</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="G16" s="14">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="H16" s="14">
         <v>30</v>
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>735</v>
+        <v>1030</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>705</v>
+        <v>410</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>55</v>
@@ -1656,21 +1671,21 @@
         <v>90</v>
       </c>
       <c r="F19" s="14">
+        <v>100</v>
+      </c>
+      <c r="G19" s="14">
         <v>2</v>
-      </c>
-      <c r="G19" s="14">
-        <v>100</v>
       </c>
       <c r="H19" s="14">
         <v>30</v>
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>707</v>
+        <v>805</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>733</v>
+        <v>635</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>64</v>
@@ -1702,21 +1717,21 @@
         <v>90</v>
       </c>
       <c r="F20" s="14">
-        <v>8</v>
+        <v>300</v>
       </c>
       <c r="G20" s="14">
-        <v>400</v>
+        <v>6</v>
       </c>
       <c r="H20" s="14">
         <v>60</v>
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>708</v>
+        <v>1000</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>732</v>
+        <v>440</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>55</v>
@@ -1731,7 +1746,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="13">
         <v>46260</v>
       </c>
@@ -1748,21 +1763,21 @@
         <v>90</v>
       </c>
       <c r="F21" s="14">
-        <v>5</v>
+        <v>400</v>
       </c>
       <c r="G21" s="14">
-        <v>250</v>
+        <v>8</v>
       </c>
       <c r="H21" s="14">
         <v>30</v>
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>680</v>
+        <v>1075</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>760</v>
+        <v>365</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>64</v>
@@ -1774,7 +1789,7 @@
         <v>51</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
@@ -1794,21 +1809,21 @@
         <v>120</v>
       </c>
       <c r="F22" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G22" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H22" s="14">
         <v>120</v>
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>945</v>
+        <v>1195</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>495</v>
+        <v>245</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>58</v>
@@ -1820,96 +1835,192 @@
         <v>60</v>
       </c>
       <c r="N22" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A23" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B23" s="14">
+        <v>500</v>
+      </c>
+      <c r="C23" s="14">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>120</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
+        <v>300</v>
+      </c>
+      <c r="G23" s="14">
+        <v>6</v>
+      </c>
+      <c r="H23" s="14">
+        <v>30</v>
+      </c>
+      <c r="I23" s="15">
+        <f t="shared" si="0"/>
+        <v>970</v>
+      </c>
+      <c r="J23" s="15">
+        <f t="shared" si="1"/>
+        <v>470</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A24" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B24" s="14">
+        <v>400</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>120</v>
+      </c>
+      <c r="E24" s="14">
+        <v>120</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>30</v>
+      </c>
+      <c r="I24" s="15">
+        <f t="shared" si="0"/>
+        <v>670</v>
+      </c>
+      <c r="J24" s="15">
+        <f t="shared" si="1"/>
+        <v>770</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A25" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B25" s="14">
+        <v>340</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14">
+        <v>240</v>
+      </c>
+      <c r="E25" s="14">
+        <v>120</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>60</v>
+      </c>
+      <c r="I25" s="15">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J25" s="15">
+        <f t="shared" si="1"/>
+        <v>680</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="M25" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A26" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B26" s="14">
+        <v>400</v>
+      </c>
+      <c r="C26" s="14">
+        <v>30</v>
+      </c>
+      <c r="D26" s="14">
+        <v>240</v>
+      </c>
+      <c r="E26" s="14">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14">
+        <v>100</v>
+      </c>
+      <c r="G26" s="14">
+        <v>2</v>
+      </c>
+      <c r="H26" s="14">
+        <v>60</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>610</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="13"/>
@@ -10190,6 +10301,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>